--- a/output/pdf_financials_xlsx/ROX.xlsx
+++ b/output/pdf_financials_xlsx/ROX.xlsx
@@ -1296,10 +1296,10 @@
         <v>-0.263241</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.343318</v>
+        <v>-0.343318</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.442096</v>
+        <v>-0.442096</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>0.347873</v>
@@ -1362,13 +1362,13 @@
         <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.695746</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0.00114</v>
+        <v>-0.54515</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.483622</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-0</v>
@@ -1600,19 +1600,19 @@
         <v>-0.263241</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.343318</v>
+        <v>-0.343318</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.442096</v>
+        <v>-0.442096</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.347873</v>
+        <v>-0.347873</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.272005</v>
+        <v>-0.272005</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.241811</v>
+        <v>-0.241811</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-0.475275</v>
@@ -1778,19 +1778,19 @@
         <v>-0.263241</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.343318</v>
+        <v>-0.343318</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.442096</v>
+        <v>-0.442096</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.347873</v>
+        <v>-0.347873</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.272005</v>
+        <v>-0.272005</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.241811</v>
+        <v>-0.241811</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-0.475275</v>
@@ -2042,10 +2042,10 @@
         <v>-0.263241</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.343318</v>
+        <v>-0.343318</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.442096</v>
+        <v>-0.442096</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>0.347873</v>
@@ -2162,10 +2162,10 @@
         <v>-0.263241</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.343498</v>
+        <v>-0.343138</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.44224</v>
+        <v>-0.441952</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0.348053</v>
@@ -2314,19 +2314,19 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.4173607424627945</v>
+        <v>199.5826392575372</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
@@ -6198,43 +6198,43 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.54575</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.5677410000000001</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.528405</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.547455</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.3547</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.235875</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.353915</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.20179</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.031699</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.583419</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.331581</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.427845</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.592984</v>
       </c>
     </row>
     <row r="93">
@@ -7706,13 +7706,13 @@
         <v>0</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>0.192078</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>0.103652</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>0.039382</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>0</v>
@@ -10503,7 +10503,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -12146,7 +12150,11 @@
           <t>Share-based payment reserve (Note 8(c))</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -13415,7 +13423,11 @@
           <t>Share-based payment reserve (Note 9(c))</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -14415,7 +14427,11 @@
           <t>Share-based payments reserve (Note 8(c))</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -15318,7 +15334,11 @@
           <t>Share-based payments reserve (Note 7(c))</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -16025,7 +16045,11 @@
           <t>Share-based payments reserve (Note 6(c))</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -17108,7 +17132,11 @@
           <t>SHARE-BASED PAYMENTS RESERVE (Note 6(c))</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -18944,7 +18972,11 @@
           <t>SHARE-BASED PAYMENTS RESERVE (Note 6) 567,741</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -20590,7 +20622,11 @@
           <t>SHARE-BASED PAYMENTS RESERVE (Note 6) 708,899</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -25476,7 +25512,11 @@
           <t>Share-based payment included in exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -28720,7 +28760,11 @@
           <t>Share-based payment included in exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -35097,7 +35141,11 @@
           <t>Change in accrued exploration and evaluation expenditures $</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -57562,10 +57610,10 @@
         </is>
       </c>
       <c r="E489" s="5" t="n">
-        <v>1.604932</v>
+        <v>-1.604932</v>
       </c>
       <c r="F489" s="5" t="n">
-        <v>0.203217</v>
+        <v>-0.203217</v>
       </c>
       <c r="G489" t="inlineStr">
         <is>
@@ -70413,19 +70461,19 @@
         </is>
       </c>
       <c r="I618" s="5" t="n">
-        <v>0.442096</v>
+        <v>-0.442096</v>
       </c>
       <c r="J618" s="5" t="n">
-        <v>0.347873</v>
+        <v>-0.347873</v>
       </c>
       <c r="K618" s="5" t="n">
-        <v>0.272005</v>
+        <v>-0.272005</v>
       </c>
       <c r="L618" s="5" t="n">
-        <v>0.241811</v>
+        <v>-0.241811</v>
       </c>
       <c r="M618" s="5" t="n">
-        <v>0.475275</v>
+        <v>-0.475275</v>
       </c>
       <c r="N618" t="inlineStr">
         <is>
@@ -72097,10 +72145,10 @@
         </is>
       </c>
       <c r="H635" s="5" t="n">
-        <v>0.343318</v>
+        <v>-0.343318</v>
       </c>
       <c r="I635" s="5" t="n">
-        <v>0.442096</v>
+        <v>-0.442096</v>
       </c>
       <c r="J635" t="inlineStr">
         <is>
@@ -72402,10 +72450,10 @@
         </is>
       </c>
       <c r="H638" s="5" t="n">
-        <v>0.305818</v>
+        <v>-0.305818</v>
       </c>
       <c r="I638" s="5" t="n">
-        <v>0.442096</v>
+        <v>-0.442096</v>
       </c>
       <c r="J638" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ROX.xlsx
+++ b/output/pdf_financials_xlsx/ROX.xlsx
@@ -1059,34 +1059,34 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.442096</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0192</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00559</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006254</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.002029</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.001472</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.003665</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>1.6e-05</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.016576</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.047233</v>
@@ -2045,34 +2045,34 @@
         <v>-0.343318</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.442096</v>
+        <v>-0.884192</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.347873</v>
+        <v>0.367073</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.273145</v>
+        <v>0.278735</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.241811</v>
+        <v>0.248065</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.475275</v>
+        <v>-0.477304</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.50877</v>
+        <v>-1.510242</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.396138</v>
+        <v>-1.399803</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-0.150551</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.426923</v>
+        <v>-1.426939</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-5.664738</v>
+        <v>-5.681314</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-5.632933</v>
@@ -2165,34 +2165,34 @@
         <v>-0.343138</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.441952</v>
+        <v>-0.8840479999999999</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.348053</v>
+        <v>0.367253</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.273601</v>
+        <v>0.279191</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.242174</v>
+        <v>0.248428</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.474984</v>
+        <v>-0.477013</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.50877</v>
+        <v>-1.510242</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.396138</v>
+        <v>-1.399803</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.150033</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.426354</v>
+        <v>-1.42637</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-5.663925</v>
+        <v>-5.680501</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-5.629013</v>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.172808</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.389045</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.172808</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.0575</v>
+        <v>0.446545</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.183408</v>
+        <v>0.0106</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.410668</v>
+        <v>0.021623</v>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -64182,7 +64182,7 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
@@ -65079,7 +65079,7 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
@@ -66976,7 +66976,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
@@ -67786,7 +67786,7 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
@@ -68689,7 +68689,7 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
@@ -70233,7 +70233,7 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
@@ -71019,7 +71019,7 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
@@ -71522,7 +71522,7 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">

--- a/output/pdf_financials_xlsx/ROX.xlsx
+++ b/output/pdf_financials_xlsx/ROX.xlsx
@@ -750,52 +750,52 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.037647</v>
+        <v>0.039165</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.031592</v>
+        <v>0.037312</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.041467</v>
+        <v>0.046405</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.079902</v>
+        <v>0.103498</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.164468</v>
+        <v>0.184831</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.149279</v>
+        <v>0.152398</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.103563</v>
+        <v>0.113356</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.136617</v>
+        <v>0.147568</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.08122500000000001</v>
+        <v>0.095947</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.13735</v>
+        <v>0.166081</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.095803</v>
+        <v>0.114524</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.156621</v>
+        <v>0.211529</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.293647</v>
+        <v>0.472053</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.322335</v>
+        <v>0.479122</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.344213</v>
+        <v>0.383434</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.485933</v>
+        <v>0.573622</v>
       </c>
     </row>
     <row r="8">
@@ -936,13 +936,13 @@
         <v>0.152955</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.041467</v>
+        <v>0.046405</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.079902</v>
+        <v>0.103498</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.164468</v>
+        <v>0.184831</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.278735</v>
@@ -996,13 +996,13 @@
         <v>-0.152955</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.041467</v>
+        <v>-0.046405</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.079902</v>
+        <v>-0.103498</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.164468</v>
+        <v>-0.184831</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>-0.278735</v>
@@ -1365,7 +1365,7 @@
         <v>-0.695746</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0.54515</v>
+        <v>0.00114</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0.483622</v>
@@ -2323,7 +2323,7 @@
         <v>200</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>199.5826392575372</v>
+        <v>0.4173607424627945</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>200</v>
@@ -7065,19 +7065,19 @@
         <v>0</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>0.859364</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>0.5701270000000001</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>0.260664</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>0.060163</v>
       </c>
       <c r="R107" s="3" t="n">
-        <v>0</v>
+        <v>0.110454</v>
       </c>
     </row>
     <row r="108">
@@ -7251,7 +7251,7 @@
         <v>0</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.008421</v>
       </c>
     </row>
     <row r="111">
@@ -7276,7 +7276,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00188</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -7291,25 +7291,25 @@
         <v>0</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002304</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001032</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.0165</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001289</v>
       </c>
       <c r="Q111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002066</v>
       </c>
     </row>
     <row r="112">
@@ -7471,16 +7471,16 @@
         <v>0</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>0</v>
+        <v>-4.00001</v>
       </c>
       <c r="O114" s="3" t="n">
-        <v>0</v>
+        <v>-12.715505</v>
       </c>
       <c r="P114" s="3" t="n">
-        <v>0</v>
+        <v>-0.775246</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>0</v>
+        <v>-1.054555</v>
       </c>
       <c r="R114" s="3" t="n">
         <v>0</v>
@@ -7496,13 +7496,13 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.044309</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -7529,16 +7529,16 @@
         <v>0</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>-4.00001</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>12.018123</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>5.1141</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.989591</v>
       </c>
       <c r="R115" s="3" t="n">
         <v>0.032166</v>
@@ -8644,7 +8644,7 @@
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00188</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -8659,25 +8659,25 @@
         <v>0</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002304</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001032</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.0165</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001289</v>
       </c>
       <c r="Q134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002066</v>
       </c>
     </row>
     <row r="135">
@@ -8702,7 +8702,7 @@
         <v>-0.201409</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.320429</v>
+        <v>-0.322309</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-0.221426</v>
@@ -8717,25 +8717,25 @@
         <v>-0.062514</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-0.419645</v>
+        <v>-0.421949</v>
       </c>
       <c r="M135" s="3" t="n">
         <v>-0.330487</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-0.302008</v>
+        <v>-0.30304</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-4.887436</v>
+        <v>-4.903936</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-4.08872</v>
+        <v>-4.090009</v>
       </c>
       <c r="Q135" s="3" t="n">
         <v>-1.205918</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-1.400466</v>
+        <v>-1.402532</v>
       </c>
     </row>
   </sheetData>
@@ -25413,7 +25413,11 @@
           <t>Share-based payment expense</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -26027,7 +26031,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -26837,7 +26845,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -28665,7 +28677,11 @@
           <t>Share-based payment expense</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -29965,7 +29981,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -30165,7 +30185,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -30264,7 +30288,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -31937,7 +31965,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -32137,7 +32169,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -32236,7 +32272,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -33248,7 +33288,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -33547,7 +33591,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -33745,7 +33793,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -33844,7 +33896,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -36341,7 +36397,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -50047,7 +50107,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -57501,7 +57565,11 @@
           <t>Future income tax (recovery) (Note 8(a))</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E488" t="inlineStr">
         <is>
           <t>-</t>
@@ -59923,7 +59991,11 @@
           <t>General and office expenses</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E512" t="inlineStr">
         <is>
           <t>-</t>
@@ -62426,7 +62498,11 @@
           <t>General and office expenses</t>
         </is>
       </c>
-      <c r="D537" t="inlineStr"/>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E537" t="inlineStr">
         <is>
           <t>-</t>
@@ -66073,7 +66149,11 @@
           <t>General and office expenses</t>
         </is>
       </c>
-      <c r="D574" t="inlineStr"/>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E574" t="inlineStr">
         <is>
           <t>-</t>
@@ -69471,7 +69551,11 @@
           <t>General and office expenses</t>
         </is>
       </c>
-      <c r="D608" t="inlineStr"/>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E608" t="inlineStr">
         <is>
           <t>-</t>
@@ -71320,7 +71404,11 @@
           <t>Income tax recovery (Note 11)</t>
         </is>
       </c>
-      <c r="D627" t="inlineStr"/>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E627" t="inlineStr">
         <is>
           <t>-</t>
